--- a/pdf2img/tabel/table_11.xlsx
+++ b/pdf2img/tabel/table_11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,214 +447,268 @@
       <c r="J1" t="n">
         <v>9</v>
       </c>
+      <c r="K1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAPORAN</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LABA</t>
+          <t>POS-POS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RUGI</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PENGHASILAN</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>KOMPREHENSIF</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>LAIN</t>
-        </is>
-      </c>
+          <t>31-Des-24</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Untuk</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>periode</t>
+          <t>Beban</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>berakhir</t>
+          <t>Bunga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>tanggal</t>
-        </is>
-      </c>
+          <t>8.602.764</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pendapatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bunga</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12.875.803</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>11.181.892</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>-~</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>woNso~wNn</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pendapatan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Beban</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Operasional</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{</t>
+          <t>LAPORAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dalain</t>
+          <t>LABA'RUGI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jutaan</t>
+          <t>DAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rupiah</t>
+          <t>PENGHASILAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>}</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>KOMPREHENSIF,</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LAIN</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Untuk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POS-POS</t>
+          <t>periode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>31-Des-24</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>berakhir</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>tanggal</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PENDAPATAN</t>
+          <t>r</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DAN</t>
+          <t>dafam</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BEBAN</t>
+          <t>jutaan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OPERASIONAL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>ruplah</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pendapatan</t>
+          <t>PENDAPATAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dan</t>
+          <t>DAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Beban</t>
+          <t>BEBAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bunga</t>
+          <t>OPERASIONAL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -663,66 +717,53 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>Pendapatan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pendapatan</t>
+          <t>dan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Beban</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Bunga</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>12.875.803</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>41.181.892</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>we</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Beban</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bunga</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>8.602.764</t>
-        </is>
-      </c>
+          <t>A25.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -732,7 +773,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(Beban}</t>
+          <t>{Beban)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -745,108 +786,111 @@
           <t>Bersih</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3.450.183</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2.579.128</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OMONAaARwWnN</t>
+          <t>Keuntungan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pendapatan</t>
+          <t>(kerugian)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dan</t>
+          <t>dari</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Beban</t>
+          <t>peningkatan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Operasional</t>
+          <t>{penurunan)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>wajar</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>keuangan</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Keuntungan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Keuntungan</t>
+          <t>(kerugian)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(kerugian)</t>
+          <t>dari</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>dari</t>
+          <t>penurunan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>peningkatan</t>
+          <t>{peningkatan)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(penurunan)</t>
+          <t>nilai</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>nilai</t>
+          <t>wajar</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>wajar</t>
+          <t>liabilitas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
           <t>keuangan</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -866,47 +910,69 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{peningkatan)</t>
+          <t>penjualan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>nilai</t>
+          <t>aset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>wajar</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>liabilitas</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
           <t>keuangan</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>penurunan</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+          <t>Keuntungan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>(kerugian)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{ransaksi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>spot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>derivalif/forward</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>{realised)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -926,23 +992,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>penjualan</t>
+          <t>penyertaan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>aset</t>
+          <t>dengan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>keuangan</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+          <t>equify</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -962,115 +1037,78 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>penjabaran</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>transaksi</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>spot</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>dan</t>
+          <t>valuta</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>derivatif/forward</t>
+          <t>asing</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(realised)</t>
+          <t>6.540</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Keuntungan</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>(kerugian)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>dari</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>penyertaan</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>dengan</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>equity</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>(kerugian)</t>
+          <t>Pendapatan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dari</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>penjabaran</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>transaksi</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>asing</t>
-        </is>
-      </c>
+          <t>dividen</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Keuntungan</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>valuta</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1079,54 +1117,57 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pendapatan</t>
+          <t>Komisi/provisi/</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>dividen</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>administrasi</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10.864</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Komisi/provisi/</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>adminisirasi</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1139,7 +1180,11 @@
           <t>lainnya</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>85.729</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1147,82 +1192,82 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kerugian</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nilai</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>keuangan</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>fimpairment)</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Kerugian</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>penurunan</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>keuangan</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>{impairment)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>171.691</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>|Kerugian</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>terkait</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>risiko</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>operasional</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1230,7 +1275,11 @@
           <t>.</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -1239,30 +1288,40 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Beban</t>
+          <t>|Kerugian</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>tenaga</t>
+          <t>terkait</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kerja</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>risiko</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>operasional</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1272,29 +1331,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>promosi</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>tenaga</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kerja</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>842.648</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Beban</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>lainnya</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -1303,19 +1367,24 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>(3.397.293)</t>
+          <t>Beban</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.523.473</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>promosi</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>47.355</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -1323,43 +1392,41 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pendapatan</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>(Beban}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Operasional</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FP</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>Beban</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>lainnya</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1.562.527</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -1367,11 +1434,12 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>55.655]</t>
+          <t>.200.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1383,26 +1451,27 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LABA</t>
+          <t>Pendapatan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(RUGI)</t>
+          <t>(Beban)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OPERASIONAL</t>
+          <t>Operasional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>_52.890|</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1411,110 +1480,126 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PENDAPATAN</t>
+          <t>LABA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>(BEBAN)</t>
+          <t>(RUGI)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NON</t>
+          <t>OPERASIONAL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OPERASIONAL</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>[</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>52890]</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>55.655)</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Keuntungan</t>
+          <t>PENDAPATAN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(kerugian)</t>
+          <t>(BEBAN)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>penjualan</t>
+          <t>NON</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>tetap</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>inventaris</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1.937</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
-      </c>
+          <t>OPERASIONAL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>(beban)</t>
+          <t>Keuntungan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>operasional</t>
+          <t>(kerugian)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>lainnya</t>
+          <t>penjualan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9.118</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>tetap</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>inventaris</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1.937</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8§20</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1524,21 +1609,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>(beban)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>non</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>operasional</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>lainnya</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>(9.118)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1567,62 +1669,69 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>LABA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>708[—S—=57.37A1|</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>(RUGI)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TAHUN</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BERJALAN</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SEBELUM</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PAJAK</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>a5q08]</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LABA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(RUGI)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>TAHUN</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BERJALAN</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>SEBELUM</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>PAJAK</t>
-        </is>
-      </c>
+          <t>57371</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1643,227 +1752,319 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>a.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Taksiran</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>pajak</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>tahun</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>berjalan</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>-/-</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>29.700</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>23.947</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>a.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+          <t>b.</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pendapatan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>(beban)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>pajak</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>tangguhan</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>{7.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>(beban)</t>
+          <t>LABA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13.966</t>
+          <t>(RUGI)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{7.854</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>BERSIH</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TAHUN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BERJALAN</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>b.</t>
+          <t>PENGHASILAN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pendapatan</t>
+          <t>KOMPREHENSIF</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>pajak</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>tangguhan</t>
-        </is>
-      </c>
+          <t>LAIN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LABA</t>
+          <t>Pos-Pos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(RUGI)</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BERSIH</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TAHUN</t>
+          <t>Akan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BERJALAN</t>
+          <t>Direklasifikasi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>29.975</t>
+          <t>ke</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>25.573</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Laba</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Rugi</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PENGHASILAN</t>
+          <t>a.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KOMPREHENSIF</t>
+          <t>Keuntungan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LAIN</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+          <t>vang</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>berasal</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>revaluasi</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>tetap</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pos-Pos</t>
+          <t>b.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Keuntungan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Akan</t>
+          <t>(kerugian}</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Direklasifikasi</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ke</t>
+          <t>berasal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Laba</t>
+          <t>dari</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rugi</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>pengukuran</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>kembali</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>atas</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>program</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+          <t>pensiun</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>manfaat</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>pasti</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -1871,47 +2072,33 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Keuntungan</t>
+          <t>c.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>berasal</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>dari</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>revaluasi</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>tetap</t>
-        </is>
-      </c>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>a.</t>
+          <t>Pos-Pos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1919,29 +2106,50 @@
           <t>yang</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Akan</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Direklasifikasi</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ke</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Laba</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Rugi</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>b.</t>
+          <t>Keuntungan</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Keuntungan</t>
+          <t>(kerugian}</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(kerugian}</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1956,198 +2164,318 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>pengukuran</t>
+          <t>penyesuaian</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>kembali</t>
+          <t>akibat</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>atas</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>penjabaran</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>laporan</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>kevangan</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>program</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+          <t>dalam</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>mata</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>uang</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>asing</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>pensiun</t>
+          <t>Keuntungan</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>manfaat</t>
+          <t>(kerugian)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>pasti</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>perubahan</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>keuangan</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>instrumen</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>hutang</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>diukur</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>pada</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>wajar</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>melalui</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>penghasilan</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>komprehensif</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>lain</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>c.</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+          <t>PENGHASILAN</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pos-Pos</t>
+          <t>KOMPREHENSIF</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Akan</t>
+          <t>LAIN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Direklasifikasi</t>
+          <t>TAHUN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ke</t>
+          <t>BERJALAN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Laba</t>
+          <t>SETELAH</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rugi</t>
+          <t>PAJAK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>(RUGI)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>KOMPREHENSIF</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>TAHUN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>BERJALAN</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Keuntungan</t>
+          <t>Laba</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(kerugian}</t>
+          <t>(Rugi)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>berasal</t>
+          <t>Bersih</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dari</t>
+          <t>Tahun</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>penyesuaian</t>
+          <t>Berjalan</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>akibat</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>penjabaran</t>
+          <t>dapat</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>laporan</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>diatribusikan</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>kepada</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2159,154 +2487,159 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>keuangan</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>dalam</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>mata</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>uang</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>asing</t>
-        </is>
-      </c>
+          <t>Pemilik</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Keuntungan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(kerugian)</t>
+          <t>Kepentingan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>dari</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>perubahan</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>nilai</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>asei</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Keuangan</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>instrumen</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>hutang</t>
-        </is>
-      </c>
+          <t>Pengendali</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>diukur</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>pada</t>
+          <t>LABA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>nilai</t>
+          <t>(RUGI)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>wajar</t>
+          <t>BERSIH</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>melalui</t>
+          <t>TAHUN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>penghasilan</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>komprehensif</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>lain</t>
-        </is>
-      </c>
+          <t>BERJALAN</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Laba</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>{Rugi)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Komprehensif</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Tahun</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Berjalan</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
           <t>yang</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>dapat</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>diatribusikan</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>kepada</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>;</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pemilik</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -2315,15 +2648,24 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PENGHASILAN</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Pengendali</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
@@ -2331,18 +2673,15 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>95.874</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>901.564</t>
-        </is>
-      </c>
+          <t>Kepentingan</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -2351,47 +2690,49 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LABA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>(RUGI)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>KOMPREHENSIF</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>LAIN</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>TAHUN</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>BERJALAN</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>SETELAH</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>PAJAK</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>TRANSFER</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2401,41 +2742,34 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>(RUGI})</t>
+          <t>(RUGI}</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KOMPREHENSIF</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TAHUN</t>
+          <t>KANTOR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BERJALAN</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>125.849</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>927.137</t>
-        </is>
-      </c>
+          <t>PUSAT</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>(Rugi)</t>
+          <t>DIVIDEN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2447,430 +2781,48 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Laba</t>
+          <t>LABA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bersih</t>
+          <t>BERSIH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tahun</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Berjalan</t>
+          <t>SAHAM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>{dalam</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>dapat</t>
+          <t>satuan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>diatribusikan</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>kepada</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
+          <t>rupiah)</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Pemilik</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Kepentingan</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Pengendali</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>LABA</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>(RUGI}</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>BERSIH</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>TAHUN</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>BERJALAN</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Laba</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>(Rugi)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Komprehensif</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Tahun</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Berjalan</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>dapat</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>diatribusikan</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>kepada</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Pemilik</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Kepentingan</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Pengendali</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>LABA</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>(RUGI)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>KOMPREHENSIF</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>TAHUN</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>BERJALAN</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TRANSFER</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>LABA</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>(RUGI}</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>KE</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>KANTOR</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>PUSAT</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>DIVIDEN</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>LABA</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>BERSIH</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>SAHAM</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>{dalam</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>satuan</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>rupiah)</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
